--- a/output/pdf_financials_xlsx/NDAT.xlsx
+++ b/output/pdf_financials_xlsx/NDAT.xlsx
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.421865</v>
+        <v>0.246947</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.275531</v>
+        <v>0.638375</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.144021</v>
+        <v>0.231666</v>
       </c>
     </row>
     <row r="11">
@@ -597,10 +597,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.354476</v>
+        <v>-0.179558</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.273978</v>
+        <v>-0.636822</v>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.024594</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.022499</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.008717000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -873,13 +873,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.155901</v>
+        <v>-0.180495</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.554476</v>
+        <v>-0.576975</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.211976</v>
+        <v>-0.220693</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.153712</v>
+        <v>-0.178306</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.552512</v>
+        <v>-0.575011</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.210117</v>
+        <v>-0.218834</v>
       </c>
     </row>
     <row r="30">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-7594.466403162055</v>
+        <v>-8809.584980237154</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-32235.23920653442</v>
+        <v>-33547.89964994165</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.7941009999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.522958</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.331196</v>
       </c>
     </row>
     <row r="35">
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.7941009999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.522958</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.331196</v>
       </c>
     </row>
     <row r="37">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.7942</v>
+        <v>9.899999999999999e-05</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.523057</v>
+        <v>9.899999999999999e-05</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.331295</v>
+        <v>9.899999999999999e-05</v>
       </c>
     </row>
     <row r="49">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">

--- a/output/pdf_financials_xlsx/NDAT.xlsx
+++ b/output/pdf_financials_xlsx/NDAT.xlsx
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.113198</v>
+        <v>0.115559</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.164697</v>
+        <v>0.172447</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.04429</v>
+        <v>0.04705</v>
       </c>
     </row>
     <row r="8">
@@ -4406,7 +4406,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="n">
         <v>0.002361</v>
       </c>
